--- a/data/seed/portfolio/L-2024-8811/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-8811/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:I185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -550,7 +550,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -560,21 +560,21 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>583000</v>
+        <v>2154000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -584,14 +584,14 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8581 от 02.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6075 01.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>01.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -601,21 +601,21 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>500000</v>
+        <v>714000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -625,14 +625,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8589 от 02.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №11/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>02.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -640,40 +640,40 @@
           <t>102</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>3797000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>10524000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Ishonch Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>229515288</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000034187509001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №57/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №912</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -683,21 +683,21 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>1298000</v>
+        <v>526000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -707,14 +707,14 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №312 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №97/26 от 03.07.2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -722,40 +722,40 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>5529000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>509000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yangi Hayot Plastik MChJ</t>
+          <t>Qarshi Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>268284206</t>
+          <t>380474717</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000469409286001</t>
+          <t>20208000631404682001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №6310</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6026 03.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -764,34 +764,39 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>9860000</v>
+        <v>3562000</v>
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Yangi Hayot Oziq-ovqat Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>211538408</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000033695746001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ЗАРАБОТНАЯ ПЛАТА ЗА ИЮНЬ 2026 Г. (ПЕРЕЧИСЛЕНИЕ НА ПЛАСТИКОВЫЕ КАРТЫ)</t>
+          <t>Tovarlar uchun to'lov h/f №8100</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>03.07.2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -799,40 +804,40 @@
           <t>106</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>607000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>22801000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7127 от 07.07.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №132/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -840,40 +845,40 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>957000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>8829000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yangi Hayot Qurilish Materiallari XK</t>
+          <t>Ishonch Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>334147187</t>
+          <t>229515288</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000609428498001</t>
+          <t>20208000034187509001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по договору №76/22</t>
+          <t>Tovar uchun to'lov, h/f №6239 06.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -883,38 +888,38 @@
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>2689000</v>
+        <v>1739000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nukus Yog' Zavodi XK</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>316360510</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000906699856001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7138 от 08.07.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4118</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -924,21 +929,21 @@
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>680000</v>
+        <v>1457000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -948,14 +953,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3531</t>
+          <t>Tovar uchun to'lov, h/f №8463 06.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -965,38 +970,38 @@
       </c>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n">
-        <v>601000</v>
+        <v>584000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Durdona Moy MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>317930687</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000602287700001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №142/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №210/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1004,40 +1009,35 @@
           <t>111</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>75706000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>9860000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Navoiy Sut Mahsulotlari AJ</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>244650189</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000500888415001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9473 от 09.07.2026, в т.ч. НДС 12%</t>
+          <t>Iyun oyi uchun ish haqi, reestr №5409</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>09.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1045,40 +1045,40 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>3527000</v>
-      </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n">
+        <v>3797000</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №51/26 от 09.07.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3244 07.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1087,39 +1087,39 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>53451000</v>
+        <v>957000</v>
       </c>
       <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Nukus Qurilish MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>346570154</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000769659685001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7910</t>
+          <t>BINO IJARASI UCHUN TO'LOV IYUL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1129,31 +1129,31 @@
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>6729000</v>
+        <v>663000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Samarqand Moy MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>380295152</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000880341875001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №278/26, QQS 12%</t>
+          <t>Shartnoma №212/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -1170,21 +1170,21 @@
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>2316000</v>
+        <v>5313000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №131/26 от 13.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №255/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -1211,31 +1211,31 @@
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>1702000</v>
+        <v>5279000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nukus Yog' Zavodi XK</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>316360510</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000906699856001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5697 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №300 13.07.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
@@ -1252,21 +1252,21 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>836000</v>
+        <v>1833000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №83/26 от 13.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7452</t>
         </is>
       </c>
     </row>
@@ -1293,21 +1293,21 @@
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>775000</v>
+        <v>1431000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4760</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5814</t>
         </is>
       </c>
     </row>
@@ -1334,38 +1334,38 @@
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>597000</v>
+        <v>1021000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Samarqand Moy MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>380295152</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000880341875001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №163/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3464 13.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1374,39 +1374,39 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>6282000</v>
+        <v>15920000</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №404</t>
+          <t>Xom ashyo uchun to'lov, shartn. №51/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1414,33 +1414,33 @@
           <t>121</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>3041000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>6918000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Termiz Qurilish Materiallari AJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>216944894</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000699046826001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №178/26</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №15/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -1457,31 +1457,31 @@
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>713000</v>
+        <v>4261000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Xiva Mato XK</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>354376925</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000581394187001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №136/26, НДС 12%</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №59/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -1496,40 +1496,40 @@
           <t>123</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>1345000</v>
-      </c>
-      <c r="D33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n">
+        <v>1241000</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4527 15.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1537,33 +1537,33 @@
           <t>124</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>1345000</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n">
+        <v>16404000</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Предоплата за товар по договору №257/26 от 16.07.2026</t>
         </is>
       </c>
     </row>
@@ -1579,39 +1579,39 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>2141000</v>
+        <v>1345000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kamalak Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>392115384</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000830336957001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №142/26 от 16.07.2026, НДС 12%</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1619,33 +1619,33 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>3893000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>1345000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Shartnoma №115/26 bo'yicha oldinan to'lov</t>
+          <t>JShDS iyun oyi uchun</t>
         </is>
       </c>
     </row>
@@ -1660,33 +1660,33 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>2695000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>14049000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №43/26 от 20.07.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №206/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -1701,33 +1701,33 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>3719000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>7269000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6561</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6662</t>
         </is>
       </c>
     </row>
@@ -1742,33 +1742,33 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>4439000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>6705000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tong Meva Eksport XK</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>275986870</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000224562718001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №200/26</t>
+          <t>Tovar uchun to'lov, h/f №4996 20.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
@@ -1783,18 +1783,23 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>16300000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>2046000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8811)</t>
+          <t>Ishonch Avto Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>229515288</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>16307000356413018417</t>
+          <t>20208000034187509001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1804,14 +1809,14 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-8811 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7075</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1819,40 +1824,40 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>1547000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>655000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>QQS iyun 2026 uchun</t>
+          <t>Mahsulot uchun to'lov, shartn. №225/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1860,40 +1865,40 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>3946000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>590000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №62/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7670</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>23.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1902,39 +1907,39 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>598000</v>
+        <v>8213000</v>
       </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000016850675001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №81/26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1942,23 +1947,18 @@
           <t>134</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>18819000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>16300000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Samarqand Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>380295152</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8811)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000880341875001</t>
+          <t>16307000356413018417</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1968,14 +1968,14 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №283/26, НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-8811 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,38 +1985,38 @@
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>3611000</v>
+        <v>1021000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Navoiy Sut Mahsulotlari AJ</t>
+          <t>Termiz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>244650189</t>
+          <t>237692515</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000500888415001</t>
+          <t>20208000139418704001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №109/26 ОТ 27.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №156/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2024,40 +2024,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>2639000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>1586000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6671 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>QQS iyun 2026 uchun</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2065,40 +2065,40 @@
           <t>137</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>720000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>6862000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tong Mebel XK</t>
+          <t>Barakali Sut AJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>397804747</t>
+          <t>362985056</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000786314046001</t>
+          <t>20208000203242531001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1802 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по договору №101/26 от 21.07.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2106,40 +2106,40 @@
           <t>138</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>4331000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>613000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №95/26</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №7461</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2147,40 +2147,40 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>987000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>4751000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nukus Yog' Zavodi XK</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>316360510</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000906699856001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3408 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №2423</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2188,40 +2188,40 @@
           <t>140</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>1892000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>17113000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Barakali Sut AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>362985056</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000203242531001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №82/26 от 31.07.2026</t>
+          <t>Tovarlar uchun to'lov h/f №6763</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>23.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2230,34 +2230,39 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>300000</v>
+        <v>4796000</v>
       </c>
       <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №296/26</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2265,23 +2270,23 @@
           <t>142</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n">
-        <v>34575000</v>
-      </c>
+      <c r="C52" s="2" t="n">
+        <v>598000</v>
+      </c>
+      <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000424712427001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2291,14 +2296,14 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №189/26 от 03.08.2026</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2308,38 +2313,38 @@
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>12195000</v>
+        <v>1497000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Yangi Hayot Moy MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>245535102</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000711734989001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Shartnoma №185/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2463</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2349,38 +2354,38 @@
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>5204000</v>
+        <v>1378000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Durdona Moy MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>317930687</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000602287700001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №65/26 от 03.08.2026</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №228/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2388,40 +2393,40 @@
           <t>145</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>9569000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>1115000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Termiz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>237692515</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000139418704001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3951</t>
+          <t>Shartnoma №289/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2430,39 +2435,39 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>7407000</v>
+        <v>2927000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Yangi Hayot Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>211538408</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000033695746001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7006</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №134/26</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>04.08.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2470,35 +2475,40 @@
           <t>147</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>10421000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>2582000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Zafar Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №9578</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3867</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2508,21 +2518,21 @@
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>8155000</v>
+        <v>2139000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2532,14 +2542,14 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8743 ОТ 05.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2488</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2549,38 +2559,38 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>3966000</v>
+        <v>619000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tong Mebel XK</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>397804747</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000786314046001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №171/26 от 05.08.2026</t>
+          <t>Mahsulot uchun to'lov, shartn. №76/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2588,40 +2598,40 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>1011000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>1174000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Yangi Hayot Qurilish Materiallari XK</t>
+          <t>Termiz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>334147187</t>
+          <t>237692515</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000609428498001</t>
+          <t>20208000139418704001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Аренда помещния за август, дог. №76/22</t>
+          <t>Mahsulot uchun to'lov, shartnoma №201/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2630,39 +2640,39 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>6420000</v>
+        <v>11280000</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №192</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №280/26</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2672,38 +2682,38 @@
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>12144000</v>
+        <v>9609000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Samarqand Moy MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>380295152</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000880341875001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №214/26 от 11.08.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9659</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2713,38 +2723,38 @@
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>5370000</v>
+        <v>3318000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Ishonch Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>229515288</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000034187509001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №11/26, НДС 12%</t>
+          <t>Shartnoma №10/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2754,38 +2764,38 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>2719000</v>
+        <v>553000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Yog' Zavodi MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>216391693</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000494088991001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9866 от 12.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №190/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2793,23 +2803,18 @@
           <t>155</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n">
-        <v>3088000</v>
-      </c>
+      <c r="C65" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Samarqand Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>380295152</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000880341875001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -2819,14 +2824,14 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №129/26 от 17.08.2026</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2834,40 +2839,40 @@
           <t>156</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>1421000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>8005000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Предоплата за товар по договору №105/26 от 03.08.2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2875,40 +2880,40 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
-        <v>1421000</v>
-      </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n">
+        <v>3187000</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6468</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2916,40 +2921,40 @@
           <t>158</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>16495000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>3052000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8055</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1108</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>18.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2957,40 +2962,40 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>11954000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>1800000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9949</t>
+          <t>Mahsulot uchun to'ov, shartnoma №287/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3000,38 +3005,38 @@
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>3249000</v>
+        <v>1165000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Ishonch Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>229515288</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000034187509001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7947 от 20.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1231</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3039,18 +3044,23 @@
           <t>161</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>16300000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>988000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8811)</t>
+          <t>Ishonch Avto Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>229515288</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>16307000356413018417</t>
+          <t>20208000034187509001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3060,14 +3070,14 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-8811 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Mahsulot uchun to'lov, shartnoma №207/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3075,40 +3085,40 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>9131000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>530000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №103/26 от 24.08.2026</t>
+          <t>Оплат за упаковочные материалы, с/ф №6514</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3118,38 +3128,38 @@
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>3581000</v>
+        <v>5303000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Qarshi Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>380474717</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000631404682001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SHARTNOMA №135/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4415 04.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3157,40 +3167,40 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>2723000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>359000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Samarqand Moy MChJ</t>
+          <t>Navro'z Sut MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>380295152</t>
+          <t>320649539</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000880341875001</t>
+          <t>20208000887662241001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №25/26 от 24.08.2026</t>
+          <t>Оплата за сырье по договору №39/26 от 04.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3199,39 +3209,39 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>632000</v>
+        <v>816000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Yangi Hayot Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>211538408</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000016850675001</t>
+          <t>20208000033695746001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за август 2026 г.</t>
+          <t>Tovarlar uchun to'lov h/f №4115</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3240,39 +3250,34 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1663000</v>
+        <v>10421000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>НДС за июль 2026 г.</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3280,23 +3285,23 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>4517000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>1174000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Qarshi Metall MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>254657015</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000776965968001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3306,14 +3311,14 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №108/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №57/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3322,39 +3327,39 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>8110000</v>
+        <v>1011000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Nukus Qurilish MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>346570154</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000769659685001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9495</t>
+          <t>Аренда помещения за август, дог. №75/22</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3364,21 +3369,21 @@
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>2891000</v>
+        <v>5401000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Samarqand Moy MChJ</t>
+          <t>Ishonch Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>380295152</t>
+          <t>229515288</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000880341875001</t>
+          <t>20208000034187509001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3388,14 +3393,14 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №194/26, НДС 12%</t>
+          <t>Оплата по с/ф №1461 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3403,40 +3408,40 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>28352000</v>
-      </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n">
+        <v>2550000</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bunyodkor Polimer MChJ</t>
+          <t>Ishonch Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>381794167</t>
+          <t>229515288</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000429647090001</t>
+          <t>20208000034187509001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Transport xizmatlri uchun to'lov, shartnoma №202/26</t>
+          <t>Shartnoma №157/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3446,38 +3451,38 @@
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>2108000</v>
+        <v>1285000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Bunyodkor Sut MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>339169374</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000408899187001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3749 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №49/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>28.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3487,38 +3492,38 @@
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>14175000</v>
+        <v>4333000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tong Mebel XK</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>397804747</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000786314046001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №4116 от 28.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по дговору №237/26 от 12.08.2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,40 +3531,40 @@
           <t>173</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>11399000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>467000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Samarqand Moy MChJ</t>
+          <t>Yangi Hayot Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>380295152</t>
+          <t>211538408</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000880341875001</t>
+          <t>20208000033695746001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Shartnoma №49/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по договору №34/26 от 14.08.2026, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3569,21 +3574,21 @@
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>1904000</v>
+        <v>10907000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3593,14 +3598,14 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №140/26, НДС 12%</t>
+          <t>Shartnoma №172/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3608,35 +3613,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>7446000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Zafar Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
+          <t>Tovar uchun to'lov, h/f №69 17.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3644,40 +3654,40 @@
           <t>176</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>6767000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>4307000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Termiz Qurilish Materiallari AJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>216944894</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000699046826001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3214</t>
+          <t>Mahsulot uchun to'lov, shartnoma №109/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3687,21 +3697,21 @@
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>2942000</v>
+        <v>3562000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nukus Yog' Zavodi XK</t>
+          <t>Bunyodkor Sut MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>316360510</t>
+          <t>339169374</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000906699856001</t>
+          <t>20208000408899187001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3711,14 +3721,14 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №218/26 от 01.09.2026</t>
+          <t>Оплата за продукцию по договору №82/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3728,21 +3738,21 @@
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>2638000</v>
+        <v>2587000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3752,14 +3762,14 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9193 за поставленный товар</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №84/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3767,40 +3777,40 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>4861000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>1608000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за транспорные услуги по дог. №3/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3765</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3810,38 +3820,38 @@
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>3522000</v>
+        <v>958000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Bunyodkor Sut MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>339169374</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000408899187001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2705 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4882 17.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3849,40 +3859,40 @@
           <t>181</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>2042000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>431000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Navro'z Sut MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>320649539</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000887662241001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №7656 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №135/26</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3890,40 +3900,40 @@
           <t>182</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>922000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>1421000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №228/26 от 04.09.2026</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3932,39 +3942,39 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>1925000</v>
+        <v>1421000</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Yangi Hayot Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>268284206</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000469409286001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7860</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3972,40 +3982,40 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>2372000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>1606000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Ishonch Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>229515288</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000034187509001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №105/26</t>
+          <t>Оплата за продукцию по договору №192/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4014,34 +4024,39 @@
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>9921000</v>
+        <v>1475000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №91/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4049,40 +4064,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>13076000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>2545000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №142/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №234/26</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4090,40 +4105,40 @@
           <t>187</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>2384000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>3767000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Xiva Mato XK</t>
+          <t>Yangi Hayot Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>354376925</t>
+          <t>211538408</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000581394187001</t>
+          <t>20208000033695746001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №257 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №185/26</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4131,40 +4146,40 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>864000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>520000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Samarqand Moy MChJ</t>
+          <t>Omad Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>380295152</t>
+          <t>279416714</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000880341875001</t>
+          <t>20208000964709003001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №6477 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №278/26</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4173,39 +4188,39 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>5949000</v>
+        <v>1643000</v>
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kamalak Plastik MChJ</t>
+          <t>Yangi Hayot Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>392115384</t>
+          <t>211538408</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000830336957001</t>
+          <t>20208000033695746001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №182/26</t>
+          <t>Tovarlar uchun to'lov h/f №8643</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4214,39 +4229,34 @@
         </is>
       </c>
       <c r="C100" s="2" t="n">
-        <v>22212000</v>
+        <v>16300000</v>
       </c>
       <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>246206495</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8811)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>16307000356413018417</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №30/26 от 07.09.2026, НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-8811 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4254,23 +4264,23 @@
           <t>191</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n">
-        <v>7718000</v>
-      </c>
+      <c r="C101" s="2" t="n">
+        <v>74088000</v>
+      </c>
+      <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Xiva Mato XK</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>354376925</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000581394187001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4280,14 +4290,14 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №160/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №218</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4297,21 +4307,21 @@
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>2386000</v>
+        <v>3165000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4321,14 +4331,14 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5520 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №213/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4338,38 +4348,38 @@
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>1661000</v>
+        <v>4425000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Durdona Moy MChJ</t>
+          <t>Ishonch Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>317930687</t>
+          <t>229515288</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000602287700001</t>
+          <t>20208000034187509001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору№40/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5248 24.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4379,38 +4389,38 @@
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>797000</v>
+        <v>3397000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Ishonch Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>229515288</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000034187509001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Shartnoma №121/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №83/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4420,38 +4430,38 @@
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>6516000</v>
+        <v>1308000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Yulduz Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>393068776</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000228770027001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Sharnoma №255/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5860 24.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4459,40 +4469,40 @@
           <t>196</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>5276000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>704000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №173/26 от 09.09.2026</t>
+          <t>Предоплата за материалы по дог. №164/26</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4501,39 +4511,39 @@
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>963000</v>
+        <v>1219000</v>
       </c>
       <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Yangi Hayot Qurilish Materiallari XK</t>
+          <t>Yangi Hayot Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>334147187</t>
+          <t>211538408</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000609428498001</t>
+          <t>20208000033695746001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>IJARA HAQI SENTYABR OYI UCHUN, SHARTNOMA №76/22</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №164/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4542,39 +4552,39 @@
         </is>
       </c>
       <c r="C108" s="2" t="n">
-        <v>2055000</v>
+        <v>1470000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8840</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №112/26</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4583,39 +4593,39 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>3016000</v>
+        <v>1664000</v>
       </c>
       <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №264/26 от 10.09.2026, НДС 12%</t>
+          <t>QQS iyul 2026 uchun</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4623,40 +4633,40 @@
           <t>200</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>12475000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>3130000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Namangan Plastik MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>328420644</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000940928641001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5621 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №15/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4664,40 +4674,40 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>1339000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>3482000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Durdona Moy MChJ</t>
+          <t>Yangi Hayot Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>317930687</t>
+          <t>211538408</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000602287700001</t>
+          <t>20208000033695746001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7743 от 11.09.2026, в т.ч. НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №213/26</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4707,38 +4717,38 @@
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>2610000</v>
+        <v>7028000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Namangan Un Mahsulotlari MChJ</t>
+          <t>Qarshi Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>350455351</t>
+          <t>380474717</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000257117349001</t>
+          <t>20208000631404682001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №2053</t>
+          <t>Mahsulot uchun to'lov, shartnoma №124/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4746,23 +4756,23 @@
           <t>203</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>1694000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Xiva Mato XK</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>354376925</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000581394187001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4772,14 +4782,14 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1552 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №58/26</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4787,40 +4797,40 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>810000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>1753000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Durdona Moy MChJ</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>317930687</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000602287700001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №45/26 от 14.09.2026</t>
+          <t>Оплата за товары согласно с/ф №4037</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4828,40 +4838,40 @@
           <t>205</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>725000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>593000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Tong Mebel XK</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>397804747</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000786314046001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9744 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №43/26</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>27.08.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4870,39 +4880,39 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>3436000</v>
+        <v>632000</v>
       </c>
       <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000424712427001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №178/26</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4912,38 +4922,38 @@
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>1550000</v>
+        <v>16007000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Qarshi Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>380474717</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000631404682001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №292/26 от 15.09.2026</t>
+          <t>Tovar uchun to'lov, h/f №4116 28.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4951,40 +4961,40 @@
           <t>208</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>4670000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>12774000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5194</t>
+          <t>Оплат за продукцию по договору №151/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4994,38 +5004,38 @@
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>23351000</v>
+        <v>6444000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Navoiy Sut Mahsulotlari AJ</t>
+          <t>Qarshi Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>244650189</t>
+          <t>380474717</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000500888415001</t>
+          <t>20208000631404682001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3142 за поставленный товар</t>
+          <t>Shartnoma №171/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5033,40 +5043,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>1353000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>8491000</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2896</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5074,40 +5084,40 @@
           <t>211</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>1353000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>4421000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>НДФЛ за август 2026</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №35/26 ОТ 31.08.2026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5115,40 +5125,35 @@
           <t>212</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>1253000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>288610738</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Shartnoma №274/26 bo'yicha oldindan to'lov</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5157,22 +5162,22 @@
         </is>
       </c>
       <c r="C123" s="2" t="n">
-        <v>6452000</v>
+        <v>352000</v>
       </c>
       <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Omad Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>279416714</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000964709003001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5182,14 +5187,14 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6009</t>
+          <t>Tovarlar uchun to'lov h/f №7853</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5197,23 +5202,23 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n">
-        <v>2171000</v>
-      </c>
+      <c r="C124" s="2" t="n">
+        <v>486000</v>
+      </c>
+      <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Xiva Mato XK</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>354376925</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000581394187001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5223,14 +5228,14 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2443 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №13/26</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5240,38 +5245,38 @@
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>904000</v>
+        <v>1377000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Xiva Mato XK</t>
+          <t>Termiz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>354376925</t>
+          <t>237692515</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000581394187001</t>
+          <t>20208000139418704001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за товар по счетфактуре №7567 от 18.09.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7935 01.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5280,34 +5285,39 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>16300000</v>
+        <v>1613000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-8811)</t>
+          <t>Omad Meva-Sabzavot AJ</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>279416714</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>16307000356413018417</t>
+          <t>20208000964709003001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-8811 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №225/26</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5316,39 +5326,39 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>1589000</v>
+        <v>6384000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Yangi Hayot Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>211538408</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000033695746001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №283/26</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5356,40 +5366,40 @@
           <t>218</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
-        <v>2338000</v>
-      </c>
-      <c r="D128" s="2" t="n"/>
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n">
+        <v>4133000</v>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tong Meva Eksport XK</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>275986870</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000224562718001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №275/26</t>
+          <t>Shartnoma №239/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5397,40 +5407,40 @@
           <t>219</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>8442000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>962000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Zafar Savdo MChJ</t>
+          <t>Bunyodkor Sut MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>246206495</t>
+          <t>339169374</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000918876622001</t>
+          <t>20208000408899187001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №94/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №204/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5440,38 +5450,38 @@
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>1345000</v>
+        <v>2303000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Samarqand Moy MChJ</t>
+          <t>Yulduz Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>380295152</t>
+          <t>393068776</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000880341875001</t>
+          <t>20208000228770027001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №4925 за поставленный товар</t>
+          <t>SHARTNOMA №152/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5479,23 +5489,23 @@
           <t>221</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
-        <v>602000</v>
-      </c>
-      <c r="D131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>1283000</v>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bunyodkor Sut MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>339169374</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000016850675001</t>
+          <t>20208000408899187001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5505,14 +5515,14 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6613 04.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5520,40 +5530,35 @@
           <t>222</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>2252000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>9921000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>288610738</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2367 от 24.09.2026, в т.ч. НДС 12%</t>
+          <t>Avgust oyi uchun ish haqi, reestr №2607</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5563,38 +5568,38 @@
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>1341000</v>
+        <v>11451000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Termiz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>237692515</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000139418704001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №127/26 от 24.09.2026</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №3342 07.09.2026, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5602,40 +5607,40 @@
           <t>224</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>2417000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>8693000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Saodat Mebel MChJ</t>
+          <t>Termiz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>288629850</t>
+          <t>237692515</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000662032425001</t>
+          <t>20208000139418704001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №224/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №145/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5645,38 +5650,38 @@
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>1256000</v>
+        <v>1147000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Denov Logistik MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>265018905</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000088841516001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2863 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №9667 ОТ 07.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5686,21 +5691,21 @@
       </c>
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="n">
-        <v>7165000</v>
+        <v>1034000</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5710,14 +5715,14 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №260/26, НДС 12%</t>
+          <t>Shartnoma №98/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5725,23 +5730,23 @@
           <t>227</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n"/>
-      <c r="D137" s="2" t="n">
-        <v>6837000</v>
-      </c>
+      <c r="C137" s="2" t="n">
+        <v>963000</v>
+      </c>
+      <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Yog' Zavodi MChJ</t>
+          <t>Nukus Qurilish MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>216391693</t>
+          <t>346570154</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000494088991001</t>
+          <t>20208000769659685001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5751,14 +5756,14 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №814 28.09.2026, QQS bilan</t>
+          <t>Bino ijarasi uchun to'lov sentyabr</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5766,40 +5771,40 @@
           <t>228</t>
         </is>
       </c>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n">
-        <v>3367000</v>
-      </c>
+      <c r="C138" s="2" t="n">
+        <v>3211000</v>
+      </c>
+      <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №275/26, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №136/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5807,40 +5812,40 @@
           <t>229</t>
         </is>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>2613000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>8501000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Nukus Yog' Zavodi XK</t>
+          <t>Omad Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>316360510</t>
+          <t>279416714</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000906699856001</t>
+          <t>20208000964709003001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7806</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №213/26</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5850,38 +5855,38 @@
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>2088000</v>
+        <v>7800000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Namangan Un Mahsulotlari MChJ</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>350455351</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000257117349001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №51/26 от 28.09.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №39/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5889,40 +5894,40 @@
           <t>231</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>1776000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>1815000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №164/26 от 28.09.2026</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA№23/26</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5930,40 +5935,40 @@
           <t>232</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>4645000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>5323000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Tong Meva Eksport XK</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>275986870</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000224562718001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8668</t>
+          <t>Shartnoma №65/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5971,40 +5976,40 @@
           <t>233</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>20276000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>965000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Tong Meva Eksport XK</t>
+          <t>Zafar Yog' Zavodi AJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>275986870</t>
+          <t>361073843</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000224562718001</t>
+          <t>20208000811014285001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №3544</t>
+          <t>Shartnoma №201/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -6012,40 +6017,40 @@
           <t>234</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>721000</v>
-      </c>
+      <c r="C144" s="2" t="n">
+        <v>1901000</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>288610738</t>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000348110142001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №35/26 ОТ 30.09.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №150/26</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -6054,53 +6059,1606 @@
         </is>
       </c>
       <c r="C145" s="2" t="n">
-        <v>300000</v>
+        <v>7960000</v>
       </c>
       <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>336051089</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000669985623001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
+          <t>Оплата за упаковочные материалы, с/ф №4306</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C146" s="4" t="n">
-        <v>389357000</v>
-      </c>
-      <c r="D146" s="4" t="n">
-        <v>399857000</v>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n">
+        <v>2104000</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Yulduz Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>393068776</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>20208000228770027001</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartn. №7/26, QQS 12%</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n">
+        <v>1983000</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Termiz Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>237692515</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>20208000139418704001</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №302 14.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>1353000</v>
+      </c>
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Ijtimoiy soliq avgust 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>1353000</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>JShDS avgust oyi uchun</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>2046000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Navro'z Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>320649539</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>20208000887662241001</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartn. №266/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>2924000</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>336051089</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>20208000669985623001</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №1152</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n">
+        <v>1629000</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Qarshi Sut Mahsulotlari AJ</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>380474717</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>20208000631404682001</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, h/f №3302 16.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>1535000</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Zafar Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>361073843</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>20208000811014285001</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №253/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n">
+        <v>2543000</v>
+      </c>
+      <c r="D154" s="2" t="n"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>336051089</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20208000669985623001</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по дог. №209/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>20.09.2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>16300000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-8811)</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>16307000356413018417</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Kredit shartnomasi L-2024-8811 bo'yicha navbatdagi to'lov (09.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>5537000</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Termiz Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>237692515</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000139418704001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Shartnoma №143/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>4325000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Bunyodkor Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>339169374</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000408899187001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Shartnoma №205/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>1375000</v>
+      </c>
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Yangi Hayot Oziq-ovqat Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>211538408</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000033695746001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №12/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="n">
+        <v>1597000</v>
+      </c>
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>QQS avgust 2026 uchun</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>2107000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Omad Meva-Sabzavot AJ</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>279416714</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000964709003001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldindan to'lov, shartn. №174/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>3612000</v>
+      </c>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>336051089</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000669985623001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №52/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>22.09.2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>2179000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>336051089</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000669985623001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №79/26, QQS BILAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>19443000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Zafar Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>361073843</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000811014285001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №68/26 от 23.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>1041000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Qarshi Sut Mahsulotlari AJ</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>380474717</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000631404682001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №219/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n">
+        <v>8539000</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Ishonch Avto Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>229515288</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>20208000034187509001</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Оплата по счет-фактуре №826 за поставленный товар</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n">
+        <v>7279000</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Zafar Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>361073843</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>20208000811014285001</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartn. №203/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n">
+        <v>1488000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Zafar Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>361073843</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>20208000811014285001</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №283</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="n">
+        <v>602000</v>
+      </c>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>20208000424712427001</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>2060000</v>
+      </c>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Omad Meva-Sabzavot AJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>279416714</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000964709003001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldndan to'lov, shartnoma №190/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>14488000</v>
+      </c>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>336051089</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000669985623001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно с/ф №3101</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>2975000</v>
+      </c>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Yangi Hayot Oziq-ovqat Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>211538408</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000033695746001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №116/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n">
+        <v>9631000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Ishonch Avto Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>229515288</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000034187509001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Оплата за товар по с/ф №6276 от 28.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n">
+        <v>6464000</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Zafar Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>361073843</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000811014285001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Оплата за товар по с/ф №2043 от 28.09.2026, в т.ч. НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n">
+        <v>3481000</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Termiz Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>237692515</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000139418704001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-fakura №7009 28.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n">
+        <v>1640000</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Zafar Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>361073843</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000811014285001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5809</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n">
+        <v>897000</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Zafar Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>361073843</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20208000811014285001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1312</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n">
+        <v>875000</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Zafar Yog' Zavodi AJ</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>361073843</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20208000811014285001</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №261/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>1085000</v>
+      </c>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Navro'z Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>320649539</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>20208000887662241001</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Transpor xizmatlari uchun to'lov, shartnoma №8/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>1499000</v>
+      </c>
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>336051089</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>20208000669985623001</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №5262</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="n">
+        <v>1744000</v>
+      </c>
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Nukus Sut Mahsulotlari MChJ</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>336051089</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>20208000669985623001</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldindan to'lov, shartn. №226/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n">
+        <v>8715000</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Yulduz Dori-Darmon MChJ</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>393068776</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>20208000228770027001</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №287/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Sarbon Moliya Bank</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Bank xizmati uchun komissiya</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>24343000</v>
+      </c>
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Barakali Sut AJ</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>362985056</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>20208000203242531001</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №154/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="n">
+        <v>393390000</v>
+      </c>
+      <c r="D184" s="4" t="n">
+        <v>403890000</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C147" s="4" t="n">
+      <c r="C185" s="4" t="n">
         <v>74500000</v>
       </c>
-      <c r="D147" s="4" t="n"/>
+      <c r="D185" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
